--- a/Output Data Tables/AFAT Outputs/Employee Tables/2017/ASMs_per_Labor_Cost_by_Airline_2017.xlsx
+++ b/Output Data Tables/AFAT Outputs/Employee Tables/2017/ASMs_per_Labor_Cost_by_Airline_2017.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30" uniqueCount="30">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -136,7 +148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -148,7 +160,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -340,6 +352,38 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>19.629999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>22.629999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>46.590000000000003</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>24.359999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>21.370000000000001</v>
       </c>
     </row>
